--- a/data/fon_listesi.xlsx
+++ b/data/fon_listesi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\enesa\Desktop\DataScience\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\enesa\Desktop\financial_analysis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8391D918-8361-4D4C-BA0B-70039369FB6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF019342-0C0E-4F15-8E7F-FB5F8417C5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1740" yWindow="1005" windowWidth="25995" windowHeight="14475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Sirket</t>
   </si>
@@ -113,6 +113,12 @@
   </si>
   <si>
     <t>XU100.IS</t>
+  </si>
+  <si>
+    <t>SMH</t>
+  </si>
+  <si>
+    <t>KOID</t>
   </si>
 </sst>
 </file>
@@ -489,7 +495,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -504,146 +510,156 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>30</v>
       </c>
     </row>
